--- a/dialbb/no_code/templates/ja/scenario.xlsx
+++ b/dialbb/no_code/templates/ja/scenario.xlsx
@@ -1,135 +1,40 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\nakano\system\dialbb\dialbb-next\dialbb\no_code\templates\ja\"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4A26A6B-39EB-40C0-9689-E4F3C13F49B4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <workbookProtection/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="scenario" sheetId="1" r:id="rId1"/>
+    <sheet name="scenario" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <definedNames/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="27">
-  <si>
-    <t>flag</t>
-  </si>
-  <si>
-    <t>state</t>
-  </si>
-  <si>
-    <t>system utterance</t>
-  </si>
-  <si>
-    <t>user utterance example</t>
-  </si>
-  <si>
-    <t>user utterance type</t>
-  </si>
-  <si>
-    <t>conditions</t>
-  </si>
-  <si>
-    <t>actions</t>
-  </si>
-  <si>
-    <t>next state</t>
-  </si>
-  <si>
-    <t>#initial</t>
-  </si>
-  <si>
-    <t>こんにちは。私はチャットボットです。よろしければお名前を教えて頂けますか？</t>
-  </si>
-  <si>
-    <t>田中です。</t>
-  </si>
-  <si>
-    <t>$ユーザが名前を言ったか判断してください$</t>
-  </si>
-  <si>
-    <t>state1</t>
-  </si>
-  <si>
-    <t>state2</t>
-  </si>
-  <si>
-    <t>state3</t>
-  </si>
-  <si>
-    <t>すみません、ちょっと理解できませんでした。今日はラーメンについて教えて下さい。ラーメンはよく食べますか？</t>
-  </si>
-  <si>
-    <t>はい、よく食べます。</t>
-  </si>
-  <si>
-    <t>$ラーメンに関する雑談を続けるために次の発話を30文字以内で生成してください。$</t>
-  </si>
-  <si>
-    <t>TT&gt;10</t>
-  </si>
-  <si>
-    <t>#final_state1</t>
-  </si>
-  <si>
-    <t>$ユーザが会話に飽きているかどうかを判断してください。$</t>
-  </si>
-  <si>
-    <t>#final_state2</t>
-  </si>
-  <si>
-    <t>$それまでの会話につづけた発話をするとともに、時間になったので会話を終わることを伝える発話を50文字で生成してください。$本日はありがとうございました。</t>
-  </si>
-  <si>
-    <t>$それまでの対話に続けて、つまらない話を続けたことを詫び、会話を終わらせてください。$本日はありがとうございました。</t>
-  </si>
-  <si>
-    <t>#error</t>
-  </si>
-  <si>
-    <t>申し訳ありません。内部エラーがおきてしまいました。今日はありがとうございました。</t>
-  </si>
-  <si>
-    <t>ありがとうございます。$ユーザの名前だけを「さん」付けで生成して。ユーザの名前以外を言うのは禁止。$、今日はラーメンについて教えて下さい。ラーメンはよく食べますか？</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="0"/>
+  <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill patternType="none"/>
+      <patternFill/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -137,44 +42,85 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+  <cellXfs count="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="標準" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <extLst>
-    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
-      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
-  </extLst>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -462,142 +408,263 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:H11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="60" customWidth="1" min="3" max="3"/>
+    <col width="24" customWidth="1" min="4" max="4"/>
+    <col width="21" customWidth="1" min="5" max="5"/>
+    <col width="30" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="15" customWidth="1" min="8" max="8"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="2" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B2" t="s">
-        <v>8</v>
-      </c>
-      <c r="C2" t="s">
-        <v>9</v>
-      </c>
-      <c r="D2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>11</v>
-      </c>
-      <c r="H2" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="3" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H3" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
-        <v>26</v>
-      </c>
-      <c r="H4" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B5" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" t="s">
-        <v>15</v>
-      </c>
-      <c r="D5" t="s">
-        <v>16</v>
-      </c>
-      <c r="H5" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B6" t="s">
-        <v>14</v>
-      </c>
-      <c r="C6" t="s">
-        <v>17</v>
-      </c>
-      <c r="F6" t="s">
-        <v>18</v>
-      </c>
-      <c r="H6" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B7" t="s">
-        <v>14</v>
-      </c>
-      <c r="F7" t="s">
-        <v>20</v>
-      </c>
-      <c r="H7" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B8" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B9" t="s">
-        <v>19</v>
-      </c>
-      <c r="C9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B10" t="s">
-        <v>21</v>
-      </c>
-      <c r="C10" t="s">
-        <v>23</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="B11" t="s">
-        <v>24</v>
-      </c>
-      <c r="C11" t="s">
-        <v>25</v>
-      </c>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>flag</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>state</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>system utterance</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>user utterance example</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>user utterance type</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>conditions</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>actions</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>next state</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr"/>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>#initial</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>こんにちは。私はチャットボットです。よろしければお名前を教えて頂けますか？</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>田中です。</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr"/>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>$ユーザが名前を言ったか判断してください$</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr"/>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>state1</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr"/>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>#initial</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr"/>
+      <c r="D3" t="inlineStr"/>
+      <c r="E3" t="inlineStr"/>
+      <c r="F3" t="inlineStr"/>
+      <c r="G3" t="inlineStr"/>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>state2</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr"/>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>state1</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ありがとうございます。$ユーザの名前だけを「さん」付けで生成して。ユーザの名前以外を言うのは禁止。$、今日はラーメンについて教えて下さい。ラーメンはよく食べますか？</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr"/>
+      <c r="E4" t="inlineStr"/>
+      <c r="F4" t="inlineStr"/>
+      <c r="G4" t="inlineStr"/>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>state3</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr"/>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>state2</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>すみません、ちょっと理解できませんでした。今日はラーメンについて教えて下さい。ラーメンはよく食べますか？</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>はい、よく食べます。</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr"/>
+      <c r="F5" t="inlineStr"/>
+      <c r="G5" t="inlineStr"/>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>state3</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr"/>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>state3</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>$ラーメンに関する雑談を続けるために次の発話を30文字以内で生成してください。$</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr"/>
+      <c r="E6" t="inlineStr"/>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>TT&gt;10</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr"/>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>#final_state1</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>state3</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr"/>
+      <c r="D7" t="inlineStr"/>
+      <c r="E7" t="inlineStr"/>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>$ユーザが会話に飽きているかどうかを判断してください。$</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr"/>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>#final_state2</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr"/>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>#final_state1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>$それまでの会話につづけた発話をするとともに、時間になったので会話を終わることを伝える発話を50文字で生成してください。$本日はありがとうございました。</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr"/>
+      <c r="G8" t="inlineStr"/>
+      <c r="H8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr"/>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>#final_state2</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>$それまでの対話に続けて、つまらない話を続けたことを詫び、会話を終わらせてください。$本日はありがとうございました。</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr"/>
+      <c r="G9" t="inlineStr"/>
+      <c r="H9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr"/>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>#error</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>申し訳ありません。内部エラーがおきてしまいました。今日はありがとうございました。</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr"/>
+      <c r="G10" t="inlineStr"/>
+      <c r="H10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
